--- a/견적서/견적서_양식.xlsx
+++ b/견적서/견적서_양식.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\cowork\견적서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBCAD1D-6055-403F-A9BF-296F5F6A6907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38A8DCD-A9C2-4980-BEB8-1AD467ED0573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28845" yWindow="16080" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HD현대삼호_견적서" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>업     태</t>
   </si>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>내부회계관리제도 IT영역 용역</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>수    량</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -114,14 +110,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>서비스</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>IT 컨설팅</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>010-9113-4578</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -131,6 +119,22 @@
   </si>
   <si>
     <t>소계</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>474-06-03501</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보통신업</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>경영 컨설팅업</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보보호 모니터링</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +864,9 @@
       <c r="H7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
@@ -874,13 +880,13 @@
         <v>6</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="32.1" customHeight="1">
@@ -895,7 +901,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -910,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>2</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="32.1" customHeight="1">
@@ -931,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -950,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="4" t="s">
@@ -965,29 +971,29 @@
     </row>
     <row r="16" spans="1:11" ht="24.95" customHeight="1">
       <c r="A16" s="19" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="16">
         <v>1</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="2">
-        <v>24000000</v>
+        <v>30000000</v>
       </c>
       <c r="J16" s="2">
         <f>I16*0.1</f>
-        <v>2400000</v>
+        <v>3000000</v>
       </c>
       <c r="K16" s="2">
         <f>(I16+J16)*G16</f>
-        <v>26400000</v>
+        <v>33000000</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="24.95" customHeight="1">
@@ -1239,7 +1245,7 @@
     </row>
     <row r="36" spans="1:11" ht="24.95" customHeight="1">
       <c r="A36" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -1252,7 +1258,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1">
         <f>SUM(K16:K35)</f>
-        <v>26400000</v>
+        <v>33000000</v>
       </c>
     </row>
   </sheetData>
